--- a/The_Den_Dragon_Scoresheet.xlsx
+++ b/The_Den_Dragon_Scoresheet.xlsx
@@ -120,7 +120,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -156,11 +156,17 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
+    <border>
+      <right/>
+      <bottom style="thin">
+        <color rgb="00333333"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -218,6 +224,49 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -595,21 +644,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>THE DEN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Dragon Scoresheet</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>9th May 2026 • The Ismaili Centre, London</t>
         </is>
@@ -617,14 +666,14 @@
     </row>
     <row r="4" ht="12" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>SCORING INSTRUCTIONS</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>1. Enter your name below  |  2. Score each founder on 5 dimensions (0–5 scale)  |  3. Refer to criteria in adjacent columns  |  4. Provide feedback</t>
         </is>
@@ -632,86 +681,86 @@
     </row>
     <row r="7" ht="12" customHeight="1"/>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>YOUR DETAILS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Dragon Name:</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
+      <c r="B9" s="32" t="n"/>
       <c r="C9" s="8" t="n"/>
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="8" t="n"/>
     </row>
     <row r="10" ht="12" customHeight="1"/>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>1. Idea &amp; Business</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Score 1</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>No clear pitch. Problem undefined or trivial. No differentiation.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Score 2</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Vague pitch. Problem lacks clarity. Generic differentiation ('we're better/cheaper').</t>
         </is>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Score 3</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Clear pitch. Credible problem. Some differentiation, plausible uniqueness.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Score 4</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Clear, engaging pitch. Real problem well-explained. Solid differentiation, good grasp of competition.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Score 5</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Sharp, memorable pitch. Urgent, validated problem. Clear competitive advantage. Strong market knowledge.</t>
         </is>
@@ -719,67 +768,67 @@
     </row>
     <row r="17" ht="8" customHeight="1"/>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>2. Progress &amp; Traction</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Score 1</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>No traction, no learning. Vague or defensive when discussing challenges.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>Score 2</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Minimal traction (idea stage or early MVP). Struggles with obstacles. Limited reflection.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Score 3</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Some early traction (pilots, early customers). Shows some resilience. Some indication of learning.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Score 4</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Good early traction with metrics (pilots, early customers, user interest). Shows resilience. Learning mindset evident.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Score 5</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>Exceptional traction (revenue, customers, growth metrics). Clear obstacles articulated. Real learning shown. Humble and coachable.</t>
         </is>
@@ -787,67 +836,67 @@
     </row>
     <row r="24" ht="8" customHeight="1"/>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t>3. Impact &amp; Responsibility</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>Score 1</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>No mention of impact or sustainability. Purely profit-focused.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>Score 2</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>Mentions impact vaguely. No metrics. Sustainability is future goal without current commitment.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>Score 3</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>Clear description of beneficiaries and outcomes. Some sustainable practices (planned or in place).</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="34" t="inlineStr">
         <is>
           <t>Score 4</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>Clear impact story with specific beneficiaries. Some measured outcomes or credible plans. Sustainability practices evident.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>Score 5</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>Impact is core to mission. Speaks with conviction about beneficiaries. Measured outcomes. Sustainability strategic and measurable.</t>
         </is>
@@ -855,67 +904,67 @@
     </row>
     <row r="31" ht="8" customHeight="1"/>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>4. Support &amp; Vision</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="34" t="inlineStr">
         <is>
           <t>Score 1</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>No clear ask or vision. Cannot articulate growth plan.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="34" t="inlineStr">
         <is>
           <t>Score 2</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>Vague support request ('money and advice'). 12-month vision unclear or unrealistic. Funding ask lacks justification.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="34" t="inlineStr">
         <is>
           <t>Score 3</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>Clear support needs aligned to stage. 12-month plan realistic with plausible outcomes. Reasonable funding ask.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="34" t="inlineStr">
         <is>
           <t>Score 4</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>Strategic support needs with clear rationale. Realistic 12-month plan with measurable outcomes. Well-reasoned funding ask.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="34" t="inlineStr">
         <is>
           <t>Score 5</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="30" t="inlineStr">
         <is>
           <t>Strategic, specific ask (mentoring, introductions, funding breakdown). Ambitious yet credible 12-month vision. Clear, measurable milestones.</t>
         </is>
@@ -923,67 +972,67 @@
     </row>
     <row r="38" ht="8" customHeight="1"/>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="33" t="inlineStr">
         <is>
           <t>5. The Founder</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>Score 1</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="30" t="inlineStr">
         <is>
           <t>No relevant experience. No palpable passion. Poor communication. Cannot defend vision credibly.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="34" t="inlineStr">
         <is>
           <t>Score 2</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="30" t="inlineStr">
         <is>
           <t>Limited relevant background. Passion unclear or overstated. Communication unclear. Defensive when challenged.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="34" t="inlineStr">
         <is>
           <t>Score 3</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="30" t="inlineStr">
         <is>
           <t>Some relevant experience. Authentic passion evident. Communicates reasonably well. Generally credible.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="34" t="inlineStr">
         <is>
           <t>Score 4</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="30" t="inlineStr">
         <is>
           <t>Some relevant background in domain. Genuine passion. Communicates well. Shows coachability and credibility.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="34" t="inlineStr">
         <is>
           <t>Score 5</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="30" t="inlineStr">
         <is>
           <t>Credible background in relevant domain. Palpable passion. Clear, engaging communication. Handles tough Q&amp;A with composure. Inspirational.</t>
         </is>
@@ -992,7 +1041,7 @@
     <row r="45" ht="8" customHeight="1"/>
     <row r="46" ht="12" customHeight="1"/>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="29" t="inlineStr">
         <is>
           <t>FOUNDER SCORES</t>
         </is>
@@ -1021,12 +1070,12 @@
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="A49" s="35" t="inlineStr">
         <is>
           <t>Founder 1</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B49" s="36" t="inlineStr">
         <is>
           <t>Idea &amp; Business</t>
         </is>
@@ -1036,7 +1085,7 @@
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="16" t="n"/>
-      <c r="B50" s="17" t="inlineStr">
+      <c r="B50" s="37" t="inlineStr">
         <is>
           <t>Progress &amp; Traction</t>
         </is>
@@ -1046,7 +1095,7 @@
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="20" t="n"/>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B51" s="36" t="inlineStr">
         <is>
           <t>Impact &amp; Responsibility</t>
         </is>
@@ -1056,7 +1105,7 @@
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="16" t="n"/>
-      <c r="B52" s="17" t="inlineStr">
+      <c r="B52" s="37" t="inlineStr">
         <is>
           <t>Support &amp; Vision</t>
         </is>
@@ -1066,7 +1115,7 @@
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="20" t="n"/>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B53" s="36" t="inlineStr">
         <is>
           <t>The Founder</t>
         </is>
@@ -1076,13 +1125,13 @@
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="21" t="inlineStr"/>
-      <c r="B54" s="22" t="inlineStr">
+      <c r="B54" s="38" t="inlineStr">
         <is>
           <t>OVERALL AVERAGE (Founder 1)</t>
         </is>
       </c>
       <c r="C54" s="23" t="n"/>
-      <c r="D54" s="24" t="inlineStr">
+      <c r="D54" s="39" t="inlineStr">
         <is>
           <t>(Average of 5 scores)</t>
         </is>
@@ -1090,12 +1139,12 @@
     </row>
     <row r="55" ht="8" customHeight="1"/>
     <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="25" t="inlineStr">
+      <c r="A56" s="40" t="inlineStr">
         <is>
           <t>Founder 2</t>
         </is>
       </c>
-      <c r="B56" s="17" t="inlineStr">
+      <c r="B56" s="37" t="inlineStr">
         <is>
           <t>Idea &amp; Business</t>
         </is>
@@ -1105,7 +1154,7 @@
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="20" t="n"/>
-      <c r="B57" s="13" t="inlineStr">
+      <c r="B57" s="36" t="inlineStr">
         <is>
           <t>Progress &amp; Traction</t>
         </is>
@@ -1115,7 +1164,7 @@
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="16" t="n"/>
-      <c r="B58" s="17" t="inlineStr">
+      <c r="B58" s="37" t="inlineStr">
         <is>
           <t>Impact &amp; Responsibility</t>
         </is>
@@ -1125,7 +1174,7 @@
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="20" t="n"/>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B59" s="36" t="inlineStr">
         <is>
           <t>Support &amp; Vision</t>
         </is>
@@ -1135,7 +1184,7 @@
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="16" t="n"/>
-      <c r="B60" s="17" t="inlineStr">
+      <c r="B60" s="37" t="inlineStr">
         <is>
           <t>The Founder</t>
         </is>
@@ -1145,13 +1194,13 @@
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="21" t="inlineStr"/>
-      <c r="B61" s="22" t="inlineStr">
+      <c r="B61" s="38" t="inlineStr">
         <is>
           <t>OVERALL AVERAGE (Founder 2)</t>
         </is>
       </c>
       <c r="C61" s="23" t="n"/>
-      <c r="D61" s="24" t="inlineStr">
+      <c r="D61" s="39" t="inlineStr">
         <is>
           <t>(Average of 5 scores)</t>
         </is>
@@ -1159,12 +1208,12 @@
     </row>
     <row r="62" ht="8" customHeight="1"/>
     <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A63" s="35" t="inlineStr">
         <is>
           <t>Founder 3</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B63" s="36" t="inlineStr">
         <is>
           <t>Idea &amp; Business</t>
         </is>
@@ -1174,7 +1223,7 @@
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="16" t="n"/>
-      <c r="B64" s="17" t="inlineStr">
+      <c r="B64" s="37" t="inlineStr">
         <is>
           <t>Progress &amp; Traction</t>
         </is>
@@ -1184,7 +1233,7 @@
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="20" t="n"/>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="B65" s="36" t="inlineStr">
         <is>
           <t>Impact &amp; Responsibility</t>
         </is>
@@ -1194,7 +1243,7 @@
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="16" t="n"/>
-      <c r="B66" s="17" t="inlineStr">
+      <c r="B66" s="37" t="inlineStr">
         <is>
           <t>Support &amp; Vision</t>
         </is>
@@ -1204,7 +1253,7 @@
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="20" t="n"/>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B67" s="36" t="inlineStr">
         <is>
           <t>The Founder</t>
         </is>
@@ -1214,13 +1263,13 @@
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="21" t="inlineStr"/>
-      <c r="B68" s="22" t="inlineStr">
+      <c r="B68" s="38" t="inlineStr">
         <is>
           <t>OVERALL AVERAGE (Founder 3)</t>
         </is>
       </c>
       <c r="C68" s="23" t="n"/>
-      <c r="D68" s="24" t="inlineStr">
+      <c r="D68" s="39" t="inlineStr">
         <is>
           <t>(Average of 5 scores)</t>
         </is>
@@ -1232,7 +1281,6 @@
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="B15:E15"/>
@@ -1265,8 +1313,9 @@
     <mergeCell ref="B44:E44"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B28:E28"/>
     <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B28:E28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
